--- a/output/laminas_comunales/comunal_o_ocup_a_2023_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2023_arica_y_parinacota.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,52 +384,622 @@
         </is>
       </c>
       <c r="C2">
-        <v>34.5858746444618</v>
+        <v>51.1012795303639</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15202</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>General Lagos</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="C3">
-        <v>30.8738425925926</v>
+        <v>51.078274078752</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Putre</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="C4">
-        <v>27.1502835538752</v>
+        <v>51.0566228799656</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>50.5050505050505</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>47.2005737159082</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>47.1606127617338</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>47.0924584792269</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>46.4419475655431</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>39.8009950248756</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>39.4889901365856</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>39.4450905220416</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>39.3877251370399</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>15102</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Camarones</t>
         </is>
       </c>
-      <c r="C5">
+      <c r="C14">
+        <v>38.1410256410256</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>36.2033195020747</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>34.7308488612836</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>34.5858746444618</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>34.5584996525161</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>34.5152313716338</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>32.2404371584699</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>30.8738425925926</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>29.8558897243108</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>29.7513245043869</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>29.7380394520655</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>29.7063786485303</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>29.1044776119403</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>27.1502835538752</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>27.1176455602685</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>27.1156681793337</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>27.0912697660608</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>26.1574074074074</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>25.9842519685039</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>24.41381495564</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>24.1046831955923</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C35">
         <v>23.9721695129665</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>23.859649122807</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>21.4333333333333</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>10.823754789272</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>10.5920432382638</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>10.5898036854667</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>10.5711949953793</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>10.0438596491228</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>7.5731981981982</v>
       </c>
     </row>
   </sheetData>
